--- a/DownloadedExcels/productPrice.xlsx
+++ b/DownloadedExcels/productPrice.xlsx
@@ -65,7 +65,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="9" max="9" style="6" width="8.0" customWidth="false"/>
@@ -163,7 +163,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20291135</t>
+          <t>65150793</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -173,22 +173,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LUX SHOWER SECRET BLISS 24X220ML</t>
+          <t>LUX SHOWER ASSORTEDPACK A01 36X220ML</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LUX SHOWER SECRET BLISS 24X220ML</t>
+          <t>LUX SHOWER ASSORTEDPACK A01 36X220ML</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>443538088VR2GGH05</t>
+          <t>443538088VR2GZZ6I</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LUXSHOWERSECRETBLISS220ML</t>
+          <t>LUX SHOWER 220ML BANDED</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -198,7 +198,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>36.00</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr">
@@ -225,6 +225,74 @@
         <v>0.0</v>
       </c>
       <c r="P2" s="2" t="n">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>65150683</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LUX SHOWER ASRT PCK LOOFA FREE 12X220ML</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LUX SHOWER ASRT PCK LOOFA FREE 12X220ML</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>443538088VR2GZZ6I</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>LUX SHOWER 220ML BANDED</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>LUX</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P3" s="2" t="n">
         <v>15.0</v>
       </c>
     </row>
